--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-synthese-medicale-sejour.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-synthese-medicale-sejour.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3194" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3194" uniqueCount="341">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -830,6 +830,10 @@
   </si>
   <si>
     <t>ED.thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
   </si>
   <si>
     <t>Observation.statusCode</t>
@@ -7347,7 +7351,7 @@
         <v>74</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>74</v>
+        <v>266</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>74</v>
@@ -7355,10 +7359,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7384,10 +7388,10 @@
         <v>91</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7418,7 +7422,7 @@
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>74</v>
@@ -7436,7 +7440,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7456,10 +7460,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7557,10 +7561,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7601,7 +7605,7 @@
         <v>74</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>74</v>
@@ -7660,10 +7664,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7763,10 +7767,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7866,10 +7870,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7969,10 +7973,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8072,10 +8076,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8173,10 +8177,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8274,10 +8278,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8377,10 +8381,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8480,10 +8484,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8583,10 +8587,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8609,13 +8613,13 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -8666,7 +8670,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -8686,10 +8690,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8712,7 +8716,7 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -8745,7 +8749,7 @@
       </c>
       <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>74</v>
@@ -8763,7 +8767,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8783,10 +8787,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8809,7 +8813,7 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
@@ -8862,7 +8866,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -8882,10 +8886,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8941,25 +8945,25 @@
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF74" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -8979,10 +8983,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9008,10 +9012,10 @@
         <v>221</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -9062,7 +9066,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -9082,10 +9086,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9108,7 +9112,7 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
@@ -9141,25 +9145,25 @@
       </c>
       <c r="Y76" s="2"/>
       <c r="Z76" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF76" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -9179,10 +9183,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9205,7 +9209,7 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
@@ -9238,25 +9242,25 @@
       </c>
       <c r="Y77" s="2"/>
       <c r="Z77" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF77" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9276,10 +9280,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9306,7 +9310,7 @@
       </c>
       <c r="L78" s="2"/>
       <c r="M78" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -9357,7 +9361,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -9377,10 +9381,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9403,7 +9407,7 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
@@ -9456,7 +9460,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -9476,10 +9480,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9502,7 +9506,7 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
@@ -9555,7 +9559,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -9575,10 +9579,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9601,7 +9605,7 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
@@ -9654,7 +9658,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -9674,10 +9678,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9700,7 +9704,7 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
@@ -9753,7 +9757,7 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -9773,10 +9777,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9799,7 +9803,7 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" s="2"/>
@@ -9852,7 +9856,7 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -9872,10 +9876,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9898,7 +9902,7 @@
         <v>74</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L84" s="2"/>
       <c r="M84" s="2"/>
@@ -9951,7 +9955,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -9971,10 +9975,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -9997,7 +10001,7 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
@@ -10050,7 +10054,7 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -10070,10 +10074,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10096,7 +10100,7 @@
         <v>74</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
@@ -10149,7 +10153,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10169,10 +10173,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10195,7 +10199,7 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
@@ -10248,7 +10252,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -10268,10 +10272,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10294,7 +10298,7 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
@@ -10347,7 +10351,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -10367,10 +10371,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10393,11 +10397,11 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L89" s="2"/>
       <c r="M89" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -10448,7 +10452,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -10468,10 +10472,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10569,10 +10573,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10670,10 +10674,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10771,10 +10775,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10872,10 +10876,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -10975,10 +10979,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11078,10 +11082,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11181,10 +11185,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11284,10 +11288,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11385,10 +11389,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11422,7 +11426,7 @@
       </c>
       <c r="Q99" s="2"/>
       <c r="R99" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="S99" t="s" s="2">
         <v>74</v>
@@ -11444,7 +11448,7 @@
       </c>
       <c r="Y99" s="2"/>
       <c r="Z99" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>74</v>
@@ -11462,7 +11466,7 @@
         <v>74</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -11482,10 +11486,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11508,7 +11512,7 @@
         <v>74</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L100" s="2"/>
       <c r="M100" s="2"/>
@@ -11561,7 +11565,7 @@
         <v>74</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>75</v>
@@ -11581,10 +11585,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11607,7 +11611,7 @@
         <v>74</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L101" s="2"/>
       <c r="M101" s="2"/>
@@ -11660,7 +11664,7 @@
         <v>74</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
